--- a/WorkBot/refactor-experimental/data/orders/Johnston Paper/Johnston Paper_Triphammer_20251114.xlsx
+++ b/WorkBot/refactor-experimental/data/orders/Johnston Paper/Johnston Paper_Triphammer_20251114.xlsx
@@ -454,20 +454,14 @@
           <t>Napkin White - Not Interfolded</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>42.00</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>42.00</t>
-        </is>
+      <c r="C2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D2" t="n">
+        <v>42</v>
+      </c>
+      <c r="E2" t="n">
+        <v>42</v>
       </c>
     </row>
   </sheetData>

--- a/WorkBot/refactor-experimental/data/orders/Johnston Paper/Johnston Paper_Triphammer_20251114.xlsx
+++ b/WorkBot/refactor-experimental/data/orders/Johnston Paper/Johnston Paper_Triphammer_20251114.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:E4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -462,6 +462,48 @@
       </c>
       <c r="E2" t="n">
         <v>42</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>86N</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Scrubbies - Green</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D3" t="n">
+        <v>6.56</v>
+      </c>
+      <c r="E3" t="n">
+        <v>6.56</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>L6070</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Lid - Deli (64oz)</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>2</v>
+      </c>
+      <c r="D4" t="n">
+        <v>85.52</v>
+      </c>
+      <c r="E4" t="n">
+        <v>171.04</v>
       </c>
     </row>
   </sheetData>
